--- a/samples/sample_04_invalid_log.xlsx
+++ b/samples/sample_04_invalid_log.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sample" sheetId="1" r:id="Rd3fcce3f9fee4ef6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sample" sheetId="1" r:id="Rade4a106ceac4503"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -293,7 +293,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5" t="str">
-        <x:v>练习：绘制多组 Raman spectra，比较 pristine、annealed 和 doped 样品的 D/G 峰变化。</x:v>
+        <x:v>练习：预设会启用对数 Y 轴、D 峰参考线和手动轴范围。</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str"/>
       <x:c r="C3" s="5" t="str"/>
@@ -302,7 +302,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="5" t="str">
-        <x:v>建议：X 轴为 raman_shift_cm，Y 轴加入三组 intensity 曲线，导出白底期刊风格图。</x:v>
+        <x:v>建议：比较 pristine、annealed 和 doped 样品在 D/G 峰附近的响应。</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str"/>
       <x:c r="C4" s="5" t="str"/>
